--- a/public/documents/pieces-defense/RF-offerts-remises-pertes.xlsx
+++ b/public/documents/pieces-defense/RF-offerts-remises-pertes.xlsx
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>462</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1013</v>
+        <v>1358</v>
       </c>
     </row>
   </sheetData>

--- a/public/documents/pieces-defense/RF-offerts-remises-pertes.xlsx
+++ b/public/documents/pieces-defense/RF-offerts-remises-pertes.xlsx
@@ -696,7 +696,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>22,8 % des achats</t>
+          <t>15,9 % des achats</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">

--- a/public/documents/pieces-defense/RF-offerts-remises-pertes.xlsx
+++ b/public/documents/pieces-defense/RF-offerts-remises-pertes.xlsx
@@ -523,31 +523,31 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Sur-versement au verre (free-pour)</t>
+          <t>Sur-versement (vins, spiritueux, cocktails)</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>807</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Crémant jeté en fin de journée</t>
+          <t>Crémant (sur-versement + jeté)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>126</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Dégustation offerte (pichet + vin nommé)</t>
+          <t>Dégustation offerte (note par note)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1358</v>
+        <v>1841</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +696,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>15,9 % des achats</t>
+          <t>11,4 % des achats</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">

--- a/public/documents/pieces-defense/RF-offerts-remises-pertes.xlsx
+++ b/public/documents/pieces-defense/RF-offerts-remises-pertes.xlsx
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1056</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="8">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1841</v>
+        <v>1843</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +696,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>11,4 % des achats</t>
+          <t>11,3 % des achats</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">

--- a/public/documents/pieces-defense/RF-offerts-remises-pertes.xlsx
+++ b/public/documents/pieces-defense/RF-offerts-remises-pertes.xlsx
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1058</v>
+        <v>720</v>
       </c>
     </row>
     <row r="8">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1843</v>
+        <v>1505</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +696,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>11,3 % des achats</t>
+          <t>14,5 % des achats</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
